--- a/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
+++ b/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\OneDrive\Documentos\FIAP\Aula\Aula_15_Normalizacao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\fiap-projetos-1tdspv\Building Relational Database\arquivos-pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70952C8-469E-4600-ADC8-8536A41B08B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205040CB-E663-4202-A817-BEC23F354A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="43">
   <si>
     <t>Data Inicio:</t>
   </si>
@@ -76,13 +74,106 @@
   </si>
   <si>
     <t>Nome Funcionario</t>
+  </si>
+  <si>
+    <t>cód projeto</t>
+  </si>
+  <si>
+    <t>data inicio</t>
+  </si>
+  <si>
+    <t>data termino</t>
+  </si>
+  <si>
+    <t>nr matricula</t>
+  </si>
+  <si>
+    <t>nome funcionario</t>
+  </si>
+  <si>
+    <t>data entrada</t>
+  </si>
+  <si>
+    <t>data saida</t>
+  </si>
+  <si>
+    <t>cod departamento</t>
+  </si>
+  <si>
+    <t>nome departamento</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>25/08/025</t>
+  </si>
+  <si>
+    <t>nome projeto</t>
+  </si>
+  <si>
+    <t>Projeto Treino</t>
+  </si>
+  <si>
+    <t>Projeto Sala</t>
+  </si>
+  <si>
+    <t>Projeto Vitrine</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>15/9/2025</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Matheus</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
+    <t>17/08/2025</t>
+  </si>
+  <si>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t>Administração</t>
+  </si>
+  <si>
+    <t>T.I</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>RH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +200,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,6 +307,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,17 +698,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE6B2DD-343E-4015-9561-87D7A7AE27D8}">
   <dimension ref="C2:H12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8" ht="15">
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
@@ -542,7 +718,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:8">
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
@@ -554,7 +730,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +742,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" ht="15">
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
@@ -576,7 +752,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8">
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -596,7 +772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:8">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -604,7 +780,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:8">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -612,7 +788,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:8">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -620,7 +796,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -628,7 +804,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -636,7 +812,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -660,42 +836,872 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B16E4B40-BD19-4268-8126-D166B1290F56}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.125" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.875" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.5">
+      <c r="A1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="9">
+        <v>22</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="30">
+        <v>45786</v>
+      </c>
+      <c r="E2" s="9">
+        <v>789456</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I2" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="9">
+        <v>25</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="9">
+        <v>759761</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I3" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="9">
+        <v>30</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="30">
+        <v>45910</v>
+      </c>
+      <c r="E4" s="9">
+        <v>761208</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10">
+        <v>22</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="11">
+        <v>45786</v>
+      </c>
+      <c r="E5" s="10">
+        <v>789456</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="10">
+        <v>3956</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="10">
+        <v>25</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="10">
+        <v>759761</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="10">
+        <v>3956</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="12">
+        <v>65</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="13">
+        <v>45786</v>
+      </c>
+      <c r="E7" s="12">
+        <v>789456</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="12">
+        <v>4599</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="12">
+        <v>65</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="13">
+        <v>45910</v>
+      </c>
+      <c r="E8" s="12">
+        <v>761208</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4599</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="14">
+        <v>78</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="15">
+        <v>45786</v>
+      </c>
+      <c r="E9" s="14">
+        <v>789456</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="33">
+        <v>45696</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="14">
+        <v>9563</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F9E3B9-033B-455C-932E-D913A6D8EF7B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.5">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="30">
+        <v>45786</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="32">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28.5">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="9">
+        <v>22</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="30">
+        <v>45786</v>
+      </c>
+      <c r="E10" s="9">
+        <v>789456</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I10" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="9">
+        <v>25</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="9">
+        <v>759761</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I11" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="9">
+        <v>30</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="30">
+        <v>45910</v>
+      </c>
+      <c r="E12" s="9">
+        <v>761208</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="30">
+        <v>45939</v>
+      </c>
+      <c r="I12" s="9">
+        <v>2564</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="10">
+        <v>22</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="11">
+        <v>45786</v>
+      </c>
+      <c r="E13" s="10">
+        <v>789456</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="10">
+        <v>3956</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="10">
+        <v>25</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="10">
+        <v>759761</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="10">
+        <v>3956</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="12">
+        <v>65</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="13">
+        <v>45786</v>
+      </c>
+      <c r="E15" s="12">
+        <v>789456</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="12">
+        <v>4599</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="12">
+        <v>65</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="13">
+        <v>45910</v>
+      </c>
+      <c r="E16" s="12">
+        <v>761208</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="12">
+        <v>4599</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="14">
+        <v>78</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="15">
+        <v>45786</v>
+      </c>
+      <c r="E17" s="14">
+        <v>789456</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="33">
+        <v>45696</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="14">
+        <v>9563</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="9">
+        <v>22</v>
+      </c>
+      <c r="B21" s="9">
+        <v>789456</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="30">
+        <v>45939</v>
+      </c>
+      <c r="F21" s="9">
+        <v>2564</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="9">
+        <v>25</v>
+      </c>
+      <c r="B22" s="9">
+        <v>759761</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="30">
+        <v>45939</v>
+      </c>
+      <c r="F22" s="9">
+        <v>2564</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="9">
+        <v>30</v>
+      </c>
+      <c r="B23" s="9">
+        <v>761208</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="30">
+        <v>45939</v>
+      </c>
+      <c r="F23" s="9">
+        <v>2564</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="10">
+        <v>22</v>
+      </c>
+      <c r="B24" s="10">
+        <v>789456</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="10">
+        <v>3956</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="10">
+        <v>25</v>
+      </c>
+      <c r="B25" s="10">
+        <v>759761</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="10">
+        <v>3956</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="12">
+        <v>65</v>
+      </c>
+      <c r="B26" s="12">
+        <v>789456</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="12">
+        <v>4599</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="12">
+        <v>65</v>
+      </c>
+      <c r="B27" s="12">
+        <v>761208</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="12">
+        <v>4599</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="14">
+        <v>78</v>
+      </c>
+      <c r="B28" s="14">
+        <v>789456</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="33">
+        <v>45696</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9563</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -703,19 +1709,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31E2949-8817-469E-AE35-24E9BBA6D515}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
@@ -726,16 +1732,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865D74B6-EFA1-46B6-996F-19377A848972}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>

--- a/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
+++ b/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\fiap-projetos-1tdspv\Building Relational Database\arquivos-pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205040CB-E663-4202-A817-BEC23F354A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589508F1-E7CD-416A-B5A5-21D667E2795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="43">
   <si>
     <t>Data Inicio:</t>
   </si>
@@ -1708,23 +1708,594 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31E2949-8817-469E-AE35-24E9BBA6D515}">
-  <dimension ref="A1"/>
+  <dimension ref="C1:M28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="3:12">
+      <c r="C1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="3:12">
+      <c r="C2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="30">
+        <v>45786</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12">
+      <c r="C3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12">
+      <c r="C4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="32">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" ht="28.5">
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12">
+      <c r="C10" s="9">
+        <v>22</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="30">
+        <v>45786</v>
+      </c>
+      <c r="G10" s="9">
+        <v>789456</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="30">
+        <v>45939</v>
+      </c>
+      <c r="K10" s="9">
+        <v>2564</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12">
+      <c r="C11" s="9">
+        <v>25</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="9">
+        <v>759761</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="30">
+        <v>45939</v>
+      </c>
+      <c r="K11" s="9">
+        <v>2564</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12">
+      <c r="C12" s="9">
+        <v>30</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="30">
+        <v>45910</v>
+      </c>
+      <c r="G12" s="9">
+        <v>761208</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="30">
+        <v>45939</v>
+      </c>
+      <c r="K12" s="9">
+        <v>2564</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12">
+      <c r="C13" s="10">
+        <v>22</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="11">
+        <v>45786</v>
+      </c>
+      <c r="G13" s="10">
+        <v>789456</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="10">
+        <v>3956</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12">
+      <c r="C14" s="10">
+        <v>25</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="10">
+        <v>759761</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="10">
+        <v>3956</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12">
+      <c r="C15" s="12">
+        <v>65</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13">
+        <v>45786</v>
+      </c>
+      <c r="G15" s="12">
+        <v>789456</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="12">
+        <v>4599</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12">
+      <c r="C16" s="12">
+        <v>65</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="13">
+        <v>45910</v>
+      </c>
+      <c r="G16" s="12">
+        <v>761208</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="12">
+        <v>4599</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13">
+      <c r="C17" s="14">
+        <v>78</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="15">
+        <v>45786</v>
+      </c>
+      <c r="G17" s="14">
+        <v>789456</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="33">
+        <v>45696</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="14">
+        <v>9563</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13">
+      <c r="C20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13">
+      <c r="C21" s="9">
+        <v>22</v>
+      </c>
+      <c r="D21" s="9">
+        <v>789456</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="30">
+        <v>45939</v>
+      </c>
+      <c r="H21" s="9">
+        <v>2564</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" s="9">
+        <v>2564</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13">
+      <c r="C22" s="9">
+        <v>25</v>
+      </c>
+      <c r="D22" s="9">
+        <v>759761</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="30">
+        <v>45939</v>
+      </c>
+      <c r="H22" s="9">
+        <v>2564</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" s="10">
+        <v>3956</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13">
+      <c r="C23" s="9">
+        <v>30</v>
+      </c>
+      <c r="D23" s="9">
+        <v>761208</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="30">
+        <v>45939</v>
+      </c>
+      <c r="H23" s="9">
+        <v>2564</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="12">
+        <v>4599</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13">
+      <c r="C24" s="10">
+        <v>22</v>
+      </c>
+      <c r="D24" s="10">
+        <v>789456</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="10">
+        <v>3956</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" s="14">
+        <v>9563</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13">
+      <c r="C25" s="10">
+        <v>25</v>
+      </c>
+      <c r="D25" s="10">
+        <v>759761</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="10">
+        <v>3956</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13">
+      <c r="C26" s="12">
+        <v>65</v>
+      </c>
+      <c r="D26" s="12">
+        <v>789456</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="12">
+        <v>4599</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13">
+      <c r="C27" s="12">
+        <v>65</v>
+      </c>
+      <c r="D27" s="12">
+        <v>761208</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="12">
+        <v>4599</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13">
+      <c r="C28" s="14">
+        <v>78</v>
+      </c>
+      <c r="D28" s="14">
+        <v>789456</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="33">
+        <v>45696</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="14">
+        <v>9563</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
+++ b/Building Relational Database/arquivos-pdf/Exercicio_Aula131.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\fiap-projetos-1tdspv\Building Relational Database\arquivos-pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589508F1-E7CD-416A-B5A5-21D667E2795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75878842-FD04-4F80-903A-FCFABC362760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{BF210B2F-CEF6-4F13-B36D-13C8A82B2CEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos" sheetId="1" r:id="rId1"/>
